--- a/templates/subtitles/campaign-2026.xlsx
+++ b/templates/subtitles/campaign-2026.xlsx
@@ -65,8 +65,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -398,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K76"/>
+  <dimension ref="A1:K123"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -716,131 +717,149 @@
       <c r="C17" t="str">
         <v>maine candidate</v>
       </c>
-      <c r="D17" t="str">
-        <v>:00</v>
-      </c>
-      <c r="E17" t="str">
-        <v>:45</v>
+      <c r="D17" s="1">
+        <v>0</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0.000038657407407407404</v>
       </c>
       <c r="F17" t="str">
-        <v>Ashley Webb</v>
+        <v>Speaker 1</v>
       </c>
       <c r="G17" t="str">
-        <v>(Candidate speaks)</v>
+        <v>Ashley Webb, what qualifications do you have to serve in the U.S.</v>
+      </c>
+      <c r="H17">
+        <v>65</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
         <v>0</v>
       </c>
-      <c r="D18" t="str">
-        <v>outro</v>
-      </c>
-      <c r="E18" t="str">
-        <v>outro</v>
+      <c r="C18" t="str">
+        <v>maine candidate</v>
+      </c>
+      <c r="D18" s="1">
+        <v>0.00004027777777777778</v>
+      </c>
+      <c r="E18" s="1">
+        <v>0.00004074074074074074</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Speaker 2</v>
       </c>
       <c r="G18" t="str">
-        <v>Vote for [Candidate X] on November 3</v>
+        <v>Senate?</v>
+      </c>
+      <c r="H18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0</v>
+      </c>
+      <c r="C19" t="str">
+        <v>maine candidate</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0.000049768518518518516</v>
+      </c>
+      <c r="E19" s="1">
+        <v>0.00007638888888888889</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Speaker 1</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Oh, I ran for office several times.</v>
+      </c>
+      <c r="H19">
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="str">
-        <v>voter id</v>
-      </c>
-      <c r="D20" t="str">
-        <v>title</v>
-      </c>
-      <c r="E20" t="str">
-        <v>title</v>
+        <v>maine candidate</v>
+      </c>
+      <c r="D20" s="1">
+        <v>0.00007777777777777778</v>
+      </c>
+      <c r="E20" s="1">
+        <v>0.00009837962962962963</v>
       </c>
       <c r="F20" t="str">
-        <v>meta data</v>
+        <v>Speaker 1</v>
       </c>
       <c r="G20" t="str">
-        <v>Who are the real election deniers?</v>
+        <v>Didn't win, but I did run.</v>
+      </c>
+      <c r="H20">
+        <v>26</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21" t="str">
-        <v>voter id</v>
-      </c>
-      <c r="D21" t="str">
-        <v>description</v>
-      </c>
-      <c r="E21" t="str">
-        <v>description</v>
+        <v>maine candidate</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0.00010023148148148148</v>
+      </c>
+      <c r="E21" s="1">
+        <v>0.00019328703703703703</v>
       </c>
       <c r="F21" t="str">
-        <v>meta data</v>
+        <v>Speaker 1</v>
       </c>
       <c r="G21" t="str">
-        <v>A battle over voter ID breaks out in a reimagined court scene from a South Asian drama.</v>
+        <v>And then I'm a songwriter and then I write my own books and then I suppose my transparency.</v>
+      </c>
+      <c r="H21">
+        <v>91</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22" t="str">
-        <v>voter id</v>
-      </c>
-      <c r="D22" t="str">
-        <v>:00</v>
-      </c>
-      <c r="E22" t="str">
-        <v>:02</v>
+        <v>maine candidate</v>
+      </c>
+      <c r="D22" s="1">
+        <v>0.00020069444444444445</v>
+      </c>
+      <c r="E22" s="1">
+        <v>0.000256712962962963</v>
       </c>
       <c r="F22" t="str">
-        <v>counsel</v>
+        <v>Speaker 1</v>
       </c>
       <c r="G22" t="str">
-        <v>Requiring an ID to vote is racist!</v>
+        <v>I wouldn't lie to the people and I wouldn't deceive the people like we're being deceived right now.</v>
+      </c>
+      <c r="H22">
+        <v>99</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>1</v>
-      </c>
-      <c r="C23" t="str">
-        <v>voter id</v>
+        <v>0</v>
       </c>
       <c r="D23" t="str">
-        <v>:03</v>
+        <v>outro</v>
       </c>
       <c r="E23" t="str">
-        <v>:06</v>
-      </c>
-      <c r="F23" t="str">
-        <v>judge</v>
+        <v>outro</v>
       </c>
       <c r="G23" t="str">
-        <v>Hey? You must explain your position.</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24">
-        <v>1</v>
-      </c>
-      <c r="C24" t="str">
-        <v>voter id</v>
-      </c>
-      <c r="D24" t="str">
-        <v>:08</v>
-      </c>
-      <c r="E24" t="str">
-        <v>:09</v>
-      </c>
-      <c r="F24" t="str">
-        <v>plaintiff</v>
-      </c>
-      <c r="G24" t="str">
-        <v>My dear mother is an example.</v>
+        <v>Vote for [Candidate X] on November 3</v>
       </c>
     </row>
     <row r="25">
@@ -851,16 +870,16 @@
         <v>voter id</v>
       </c>
       <c r="D25" t="str">
-        <v>:09</v>
+        <v>title</v>
       </c>
       <c r="E25" t="str">
-        <v>:10</v>
+        <v>title</v>
       </c>
       <c r="F25" t="str">
-        <v>judge</v>
+        <v>meta data</v>
       </c>
       <c r="G25" t="str">
-        <v>That is so?</v>
+        <v>Who are the real election deniers?</v>
       </c>
     </row>
     <row r="26">
@@ -871,16 +890,16 @@
         <v>voter id</v>
       </c>
       <c r="D26" t="str">
-        <v>:10</v>
+        <v>description</v>
       </c>
       <c r="E26" t="str">
-        <v>:11</v>
+        <v>description</v>
       </c>
       <c r="F26" t="str">
-        <v>plaintiff</v>
+        <v>meta data</v>
       </c>
       <c r="G26" t="str">
-        <v>She has no one to take her to the DMV.</v>
+        <v>A battle over voter ID breaks out in a reimagined court scene from a South Asian drama.</v>
       </c>
     </row>
     <row r="27">
@@ -891,16 +910,16 @@
         <v>voter id</v>
       </c>
       <c r="D27" t="str">
-        <v>:11</v>
+        <v>:00</v>
       </c>
       <c r="E27" t="str">
-        <v>:15</v>
+        <v>:02</v>
       </c>
       <c r="F27" t="str">
-        <v>judge</v>
+        <v>counsel</v>
       </c>
       <c r="G27" t="str">
-        <v>Why don't you take her? She can get a photo ID without cost!</v>
+        <v>Requiring an ID to vote is racist!</v>
       </c>
     </row>
     <row r="28">
@@ -911,16 +930,16 @@
         <v>voter id</v>
       </c>
       <c r="D28" t="str">
-        <v>:15</v>
+        <v>:03</v>
       </c>
       <c r="E28" t="str">
-        <v>:16</v>
+        <v>:06</v>
       </c>
       <c r="F28" t="str">
-        <v>counsel</v>
+        <v>judge</v>
       </c>
       <c r="G28" t="str">
-        <v>No.</v>
+        <v>Hey? You must explain your position.</v>
       </c>
     </row>
     <row r="29">
@@ -931,16 +950,16 @@
         <v>voter id</v>
       </c>
       <c r="D29" t="str">
-        <v>:17</v>
+        <v>:08</v>
       </c>
       <c r="E29" t="str">
-        <v>:22</v>
+        <v>:09</v>
       </c>
       <c r="F29" t="str">
-        <v>judge</v>
+        <v>plaintiff</v>
       </c>
       <c r="G29" t="str">
-        <v>No? There is nothing preventing her from getting one.</v>
+        <v>My dear mother is an example.</v>
       </c>
     </row>
     <row r="30">
@@ -951,16 +970,16 @@
         <v>voter id</v>
       </c>
       <c r="D30" t="str">
-        <v>:23</v>
+        <v>:09</v>
       </c>
       <c r="E30" t="str">
-        <v>:25</v>
+        <v>:10</v>
       </c>
       <c r="F30" t="str">
-        <v>counsel</v>
+        <v>judge</v>
       </c>
       <c r="G30" t="str">
-        <v>But what if her bursitis flares up?</v>
+        <v>That is so?</v>
       </c>
     </row>
     <row r="31">
@@ -971,16 +990,16 @@
         <v>voter id</v>
       </c>
       <c r="D31" t="str">
-        <v>:26</v>
+        <v>:10</v>
       </c>
       <c r="E31" t="str">
-        <v>:28</v>
+        <v>:11</v>
       </c>
       <c r="F31" t="str">
-        <v>judge</v>
+        <v>plaintiff</v>
       </c>
       <c r="G31" t="str">
-        <v>You Democrats are making yourselves very clear now.</v>
+        <v>She has no one to take her to the DMV.</v>
       </c>
     </row>
     <row r="32">
@@ -991,16 +1010,16 @@
         <v>voter id</v>
       </c>
       <c r="D32" t="str">
-        <v>:29</v>
+        <v>:11</v>
       </c>
       <c r="E32" t="str">
-        <v>:33</v>
+        <v>:15</v>
       </c>
       <c r="F32" t="str">
         <v>judge</v>
       </c>
       <c r="G32" t="str">
-        <v>It's not Donald Trump who wants to end elections.</v>
+        <v>Why don't you take her? She can get a photo ID without cost!</v>
       </c>
     </row>
     <row r="33">
@@ -1011,16 +1030,16 @@
         <v>voter id</v>
       </c>
       <c r="D33" t="str">
-        <v>outro</v>
+        <v>:15</v>
       </c>
       <c r="E33" t="str">
-        <v>outro</v>
+        <v>:16</v>
       </c>
       <c r="F33" t="str">
-        <v>black screen</v>
+        <v>counsel</v>
       </c>
       <c r="G33" t="str">
-        <v>Protect your vote</v>
+        <v>No.</v>
       </c>
     </row>
     <row r="34">
@@ -1031,79 +1050,105 @@
         <v>voter id</v>
       </c>
       <c r="D34" t="str">
-        <v>outro</v>
+        <v>:17</v>
       </c>
       <c r="E34" t="str">
-        <v>outro</v>
+        <v>:22</v>
       </c>
       <c r="F34" t="str">
-        <v>black screen</v>
+        <v>judge</v>
       </c>
       <c r="G34" t="str">
-        <v>Vote for Republican  [Candidate X] on November 3</v>
+        <v>No? There is nothing preventing her from getting one.</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>1</v>
+      </c>
+      <c r="C35" t="str">
+        <v>voter id</v>
+      </c>
+      <c r="D35" t="str">
+        <v>:23</v>
+      </c>
+      <c r="E35" t="str">
+        <v>:25</v>
+      </c>
+      <c r="F35" t="str">
+        <v>counsel</v>
+      </c>
+      <c r="G35" t="str">
+        <v>But what if her bursitis flares up?</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C36" t="str">
-        <v>bollywood action</v>
+        <v>voter id</v>
       </c>
       <c r="D36" t="str">
-        <v>title</v>
+        <v>:26</v>
       </c>
       <c r="E36" t="str">
-        <v>title</v>
+        <v>:28</v>
       </c>
       <c r="F36" t="str">
-        <v>meta data</v>
+        <v>judge</v>
       </c>
       <c r="G36" t="str">
-        <v>Law enforcement you can count on.</v>
+        <v>You Democrats are making yourselves very clear now.</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C37" t="str">
-        <v>bollywood action</v>
+        <v>voter id</v>
       </c>
       <c r="D37" t="str">
-        <v>description</v>
+        <v>:29</v>
       </c>
       <c r="E37" t="str">
-        <v>description</v>
+        <v>:33</v>
       </c>
       <c r="F37" t="str">
-        <v>meta data</v>
+        <v>judge</v>
       </c>
       <c r="G37" t="str">
-        <v>A law-enforcement officer goes to extraordinary, against-all-odds lengths to protect his citizens.</v>
+        <v>It's not Donald Trump who wants to end elections.</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C38" t="str">
-        <v>bollywood action</v>
+        <v>voter id</v>
       </c>
       <c r="D38" t="str">
-        <v>:00</v>
+        <v>outro</v>
       </c>
       <c r="E38" t="str">
-        <v>:38</v>
+        <v>outro</v>
       </c>
       <c r="F38" t="str">
-        <v>Law-enforcement officer (insert Republican candidate's head)</v>
+        <v>black screen</v>
       </c>
       <c r="G38" t="str">
-        <v>none</v>
+        <v>Protect your vote</v>
       </c>
     </row>
     <row r="39">
+      <c r="A39">
+        <v>1</v>
+      </c>
+      <c r="C39" t="str">
+        <v>voter id</v>
+      </c>
       <c r="D39" t="str">
         <v>outro</v>
       </c>
@@ -1114,27 +1159,27 @@
         <v>black screen</v>
       </c>
       <c r="G39" t="str">
-        <v>Safety. Security. Law enforcement you can count on.</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40">
+        <v>Vote for Republican  [Candidate X] on November 3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
         <v>3</v>
       </c>
-      <c r="C40" t="str">
+      <c r="C41" t="str">
         <v>bollywood action</v>
       </c>
-      <c r="D40" t="str">
-        <v>outro</v>
-      </c>
-      <c r="E40" t="str">
-        <v>outro</v>
-      </c>
-      <c r="F40" t="str">
-        <v>black screen</v>
-      </c>
-      <c r="G40" t="str">
-        <v>Vote for Republican  [Candidate X] on November 3</v>
+      <c r="D41" t="str">
+        <v>title</v>
+      </c>
+      <c r="E41" t="str">
+        <v>title</v>
+      </c>
+      <c r="F41" t="str">
+        <v>meta data</v>
+      </c>
+      <c r="G41" t="str">
+        <v>Law enforcement you can count on.</v>
       </c>
     </row>
     <row r="42">
@@ -1142,39 +1187,33 @@
         <v>3</v>
       </c>
       <c r="C42" t="str">
-        <v>buried alive</v>
+        <v>bollywood action</v>
       </c>
       <c r="D42" t="str">
-        <v>title</v>
+        <v>description</v>
       </c>
       <c r="E42" t="str">
-        <v>title</v>
+        <v>description</v>
       </c>
       <c r="F42" t="str">
         <v>meta data</v>
       </c>
       <c r="G42" t="str">
-        <v>Democrats mourn the death of the Constitution</v>
+        <v>A law-enforcement officer goes to extraordinary, against-all-odds lengths to protect his citizens.</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>3</v>
-      </c>
-      <c r="C43" t="str">
-        <v>buried alive</v>
-      </c>
       <c r="D43" t="str">
-        <v>description</v>
+        <v>outro</v>
       </c>
       <c r="E43" t="str">
-        <v>description</v>
+        <v>outro</v>
       </c>
       <c r="F43" t="str">
-        <v>meta data</v>
+        <v>black screen</v>
       </c>
       <c r="G43" t="str">
-        <v>A burial scene from a Filipino telenovela illustrates what Democrats really think about the Constitution.</v>
+        <v>Safety. Security. Law enforcement you can count on.</v>
       </c>
     </row>
     <row r="44">
@@ -1182,39 +1221,19 @@
         <v>3</v>
       </c>
       <c r="C44" t="str">
-        <v>buried alive</v>
+        <v>bollywood action</v>
       </c>
       <c r="D44" t="str">
-        <v>intro</v>
+        <v>outro</v>
       </c>
       <c r="E44" t="str">
-        <v>intro</v>
+        <v>outro</v>
       </c>
       <c r="F44" t="str">
         <v>black screen</v>
       </c>
       <c r="G44" t="str">
-        <v>Democrats mourn the death of the Constitution</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45">
-        <v>3</v>
-      </c>
-      <c r="C45" t="str">
-        <v>buried alive</v>
-      </c>
-      <c r="D45" t="str">
-        <v>:00</v>
-      </c>
-      <c r="E45" t="str">
-        <v>:19</v>
-      </c>
-      <c r="F45" t="str">
-        <v>Fake mourner</v>
-      </c>
-      <c r="G45" t="str">
-        <v>no added text</v>
+        <v>Vote for Republican  [Candidate X] on November 3</v>
       </c>
     </row>
     <row r="46">
@@ -1225,16 +1244,16 @@
         <v>buried alive</v>
       </c>
       <c r="D46" t="str">
-        <v>outro</v>
+        <v>title</v>
       </c>
       <c r="E46" t="str">
-        <v>outro</v>
+        <v>title</v>
       </c>
       <c r="F46" t="str">
-        <v>black screen</v>
+        <v>meta data</v>
       </c>
       <c r="G46" t="str">
-        <v>Vote like your life depends on it.</v>
+        <v>Democrats mourn the death of the Constitution</v>
       </c>
     </row>
     <row r="47">
@@ -1245,113 +1264,122 @@
         <v>buried alive</v>
       </c>
       <c r="D47" t="str">
-        <v>outro</v>
+        <v>description</v>
       </c>
       <c r="E47" t="str">
-        <v>outro</v>
+        <v>description</v>
       </c>
       <c r="F47" t="str">
+        <v>meta data</v>
+      </c>
+      <c r="G47" t="str">
+        <v>A burial scene from a Filipino telenovela illustrates what Democrats really think about the Constitution.</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>3</v>
+      </c>
+      <c r="C48" t="str">
+        <v>buried alive</v>
+      </c>
+      <c r="D48" t="str">
+        <v>intro</v>
+      </c>
+      <c r="E48" t="str">
+        <v>intro</v>
+      </c>
+      <c r="F48" t="str">
         <v>black screen</v>
       </c>
-      <c r="G47" t="str">
-        <v>Vote for Republican  [Candidate X] on November 3</v>
+      <c r="G48" t="str">
+        <v>Democrats mourn the death of the Constitution</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C49" t="str">
-        <v>save the day</v>
-      </c>
-      <c r="D49" t="str">
-        <v>title</v>
-      </c>
-      <c r="E49" t="str">
-        <v>title</v>
+        <v>buried alive</v>
+      </c>
+      <c r="D49" s="1">
+        <v>0.0001480324074074074</v>
+      </c>
+      <c r="E49" s="1">
+        <v>0.00016099537037037037</v>
       </c>
       <c r="F49" t="str">
-        <v>meta data</v>
+        <v>Speaker 1</v>
       </c>
       <c r="G49" t="str">
-        <v>There's one thing that Democrats and Republicans can agree on.</v>
+        <v>Don't stop!</v>
+      </c>
+      <c r="H49">
+        <v>11</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C50" t="str">
-        <v>save the day</v>
-      </c>
-      <c r="D50" t="str">
-        <v>description</v>
-      </c>
-      <c r="E50" t="str">
-        <v>description</v>
+        <v>buried alive</v>
+      </c>
+      <c r="D50" s="1">
+        <v>0.00016724537037037036</v>
+      </c>
+      <c r="E50" s="1">
+        <v>0.0001744212962962963</v>
       </c>
       <c r="F50" t="str">
-        <v>meta data</v>
+        <v>Speaker 2</v>
       </c>
       <c r="G50" t="str">
-        <v>An ad in the Democrats'  famous 2016 Save the Day campaign is reworked for the 2026 midterms</v>
+        <v>Go on!</v>
+      </c>
+      <c r="H50">
+        <v>6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C51" t="str">
-        <v>save the day</v>
+        <v>buried alive</v>
       </c>
       <c r="D51" t="str">
-        <v>intro</v>
+        <v>outro</v>
       </c>
       <c r="E51" t="str">
-        <v>intro</v>
+        <v>outro</v>
       </c>
       <c r="F51" t="str">
         <v>black screen</v>
       </c>
       <c r="G51" t="str">
-        <v>Democrats are right for once …</v>
+        <v>Vote like your life depends on it.</v>
       </c>
     </row>
     <row r="52">
       <c r="A52">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C52" t="str">
-        <v>save the day</v>
+        <v>buried alive</v>
       </c>
       <c r="D52" t="str">
-        <v>:00</v>
+        <v>outro</v>
       </c>
       <c r="E52" t="str">
-        <v>:30</v>
+        <v>outro</v>
+      </c>
+      <c r="F52" t="str">
+        <v>black screen</v>
       </c>
       <c r="G52" t="str">
-        <v>Democrat celebs speak</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>0</v>
-      </c>
-      <c r="C53" t="str">
-        <v>save the day</v>
-      </c>
-      <c r="D53" t="str">
-        <v>outro</v>
-      </c>
-      <c r="E53" t="str">
-        <v>outro</v>
-      </c>
-      <c r="F53" t="str">
-        <v>black screen</v>
-      </c>
-      <c r="G53" t="str">
-        <v>There's at least one thing we can agree on ...</v>
+        <v>Vote for Republican  [Candidate X] on November 3</v>
       </c>
     </row>
     <row r="54">
@@ -1362,16 +1390,16 @@
         <v>save the day</v>
       </c>
       <c r="D54" t="str">
-        <v>outro</v>
+        <v>title</v>
       </c>
       <c r="E54" t="str">
-        <v>outro</v>
+        <v>title</v>
       </c>
       <c r="F54" t="str">
-        <v>black screen</v>
+        <v>meta data</v>
       </c>
       <c r="G54" t="str">
-        <v>"We cannot pretend both sides are equally unfavorable."</v>
+        <v>There's one thing that Democrats and Republicans can agree on.</v>
       </c>
     </row>
     <row r="55">
@@ -1382,16 +1410,36 @@
         <v>save the day</v>
       </c>
       <c r="D55" t="str">
-        <v>outro</v>
+        <v>description</v>
       </c>
       <c r="E55" t="str">
-        <v>outro</v>
+        <v>description</v>
       </c>
       <c r="F55" t="str">
+        <v>meta data</v>
+      </c>
+      <c r="G55" t="str">
+        <v>An ad in the Democrats'  famous 2016 Save the Day campaign is reworked for the 2026 midterms</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0</v>
+      </c>
+      <c r="C56" t="str">
+        <v>save the day</v>
+      </c>
+      <c r="D56" t="str">
+        <v>intro</v>
+      </c>
+      <c r="E56" t="str">
+        <v>intro</v>
+      </c>
+      <c r="F56" t="str">
         <v>black screen</v>
       </c>
-      <c r="G55" t="str">
-        <v>Vote for Republican [Candidate X] on November 3</v>
+      <c r="G56" t="str">
+        <v>Democrats are right for once …</v>
       </c>
     </row>
     <row r="57">
@@ -1399,213 +1447,298 @@
         <v>0</v>
       </c>
       <c r="C57" t="str">
-        <v>chicken little</v>
-      </c>
-      <c r="D57" t="str">
-        <v>title</v>
-      </c>
-      <c r="E57" t="str">
-        <v>title</v>
+        <v>save the day</v>
+      </c>
+      <c r="D57" s="1">
+        <v>0</v>
+      </c>
+      <c r="E57" s="1">
+        <v>0.00002337962962962963</v>
       </c>
       <c r="F57" t="str">
-        <v>meta data</v>
+        <v>Speaker 1</v>
       </c>
       <c r="G57" t="str">
-        <v>The new star of the Democratic Party looks familiar</v>
+        <v>We can save the day.</v>
+      </c>
+      <c r="H57">
+        <v>20</v>
       </c>
     </row>
     <row r="58">
       <c r="A58">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C58" t="str">
-        <v>chicken little</v>
-      </c>
-      <c r="D58" t="str">
-        <v>description</v>
-      </c>
-      <c r="E58" t="str">
-        <v>description</v>
+        <v>save the day</v>
+      </c>
+      <c r="D58" s="1">
+        <v>0.000026157407407407405</v>
+      </c>
+      <c r="E58" s="1">
+        <v>0.00003287037037037037</v>
       </c>
       <c r="F58" t="str">
-        <v>meta data</v>
+        <v>Speaker 1</v>
       </c>
       <c r="G58" t="str">
-        <v>Border walls are useless when the enemy is within, as these clips from the 1943 Disney cartoon Chicken Little illustrate.</v>
+        <v>For our children.</v>
+      </c>
+      <c r="H58">
+        <v>17</v>
       </c>
     </row>
     <row r="59">
       <c r="A59">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C59" t="str">
-        <v>chicken little</v>
-      </c>
-      <c r="D59" t="str">
-        <v>:00</v>
-      </c>
-      <c r="E59">
-        <v>0.041666666666666664</v>
+        <v>save the day</v>
+      </c>
+      <c r="D59" s="1">
+        <v>0.000033796296296296295</v>
+      </c>
+      <c r="E59" s="1">
+        <v>0.00004050925925925926</v>
       </c>
       <c r="F59" t="str">
-        <v>Insert cartoon head of Mamdani on Foxy Loxy</v>
+        <v>Speaker 2</v>
       </c>
       <c r="G59" t="str">
-        <v>cartoon with no text</v>
+        <v>For our children.</v>
+      </c>
+      <c r="H59">
+        <v>17</v>
       </c>
     </row>
     <row r="60">
       <c r="A60">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C60" t="str">
-        <v>chicken little</v>
-      </c>
-      <c r="D60" t="str">
-        <v>outro</v>
-      </c>
-      <c r="E60" t="str">
-        <v>outro</v>
+        <v>save the day</v>
+      </c>
+      <c r="D60" s="1">
+        <v>0.00004212962962962963</v>
+      </c>
+      <c r="E60" s="1">
+        <v>0.000049074074074074075</v>
       </c>
       <c r="F60" t="str">
-        <v>black screen</v>
+        <v>Speaker 2</v>
       </c>
       <c r="G60" t="str">
-        <v>Vote as if your life depends on it.</v>
+        <v>For our children.</v>
+      </c>
+      <c r="H60">
+        <v>17</v>
       </c>
     </row>
     <row r="61">
       <c r="A61">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C61" t="str">
-        <v>chicken little</v>
-      </c>
-      <c r="D61" t="str">
-        <v>outro</v>
-      </c>
-      <c r="E61" t="str">
-        <v>outro</v>
+        <v>save the day</v>
+      </c>
+      <c r="D61" s="1">
+        <v>0.00005069444444444444</v>
+      </c>
+      <c r="E61" s="1">
+        <v>0.0000587962962962963</v>
       </c>
       <c r="F61" t="str">
-        <v>black screen</v>
+        <v>Speaker 1</v>
       </c>
       <c r="G61" t="str">
-        <v>Vote for Republican [Candidate X] on November 3</v>
+        <v>For our communities.</v>
+      </c>
+      <c r="H61">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0</v>
+      </c>
+      <c r="C62" t="str">
+        <v>save the day</v>
+      </c>
+      <c r="D62" s="1">
+        <v>0.0000699074074074074</v>
+      </c>
+      <c r="E62" s="1">
+        <v>0.00007824074074074074</v>
+      </c>
+      <c r="F62" t="str">
+        <v>Speaker 2</v>
+      </c>
+      <c r="G62" t="str">
+        <v>For our communities.</v>
+      </c>
+      <c r="H62">
+        <v>20</v>
       </c>
     </row>
     <row r="63">
       <c r="A63">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C63" t="str">
-        <v>korea rain</v>
-      </c>
-      <c r="D63" t="str">
-        <v>title</v>
-      </c>
-      <c r="E63" t="str">
-        <v>title</v>
+        <v>save the day</v>
+      </c>
+      <c r="D63" s="1">
+        <v>0.00008171296296296296</v>
+      </c>
+      <c r="E63" s="1">
+        <v>0.00009050925925925927</v>
       </c>
       <c r="F63" t="str">
-        <v>meta data</v>
+        <v>Speaker 1</v>
       </c>
       <c r="G63" t="str">
-        <v>Impressed with your leaders?</v>
+        <v>For America.</v>
+      </c>
+      <c r="H63">
+        <v>12</v>
       </c>
     </row>
     <row r="64">
       <c r="A64">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C64" t="str">
-        <v>korea rain</v>
-      </c>
-      <c r="D64" t="str">
-        <v>description</v>
-      </c>
-      <c r="E64" t="str">
-        <v>description</v>
+        <v>save the day</v>
+      </c>
+      <c r="D64" s="1">
+        <v>0.00009212962962962963</v>
+      </c>
+      <c r="E64" s="1">
+        <v>0.00009976851851851851</v>
       </c>
       <c r="F64" t="str">
-        <v>meta data</v>
+        <v>Speaker 1</v>
       </c>
       <c r="G64" t="str">
-        <v>A man tries to impress a woman with an idea for protecting her from the rain. She has the real solution.</v>
+        <v>For America.</v>
+      </c>
+      <c r="H64">
+        <v>12</v>
       </c>
     </row>
     <row r="65">
       <c r="A65">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C65" t="str">
-        <v>korea rain</v>
-      </c>
-      <c r="D65" t="str">
-        <v>intro</v>
-      </c>
-      <c r="E65" t="str">
-        <v>intro</v>
+        <v>save the day</v>
+      </c>
+      <c r="D65" s="1">
+        <v>0.0001011574074074074</v>
+      </c>
+      <c r="E65" s="1">
+        <v>0.00010833333333333333</v>
       </c>
       <c r="F65" t="str">
-        <v>black screen</v>
+        <v>Speaker 2</v>
       </c>
       <c r="G65" t="str">
-        <v>Democrat [CandidateX] wants to impress you.</v>
+        <v>For America.</v>
+      </c>
+      <c r="H65">
+        <v>12</v>
       </c>
     </row>
     <row r="66">
       <c r="A66">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C66" t="str">
-        <v>korea rain</v>
+        <v>save the day</v>
+      </c>
+      <c r="D66" s="1">
+        <v>0.00011921296296296297</v>
+      </c>
+      <c r="E66" s="1">
+        <v>0.00014699074074074075</v>
       </c>
       <c r="F66" t="str">
-        <v>Insert candidates heads. Democrat is man. Republican is woman.</v>
+        <v>Speaker 2</v>
       </c>
       <c r="G66" t="str">
-        <v>Man and woman converse (actual subtitles)</v>
+        <v>All it takes is all of us.</v>
+      </c>
+      <c r="H66">
+        <v>26</v>
       </c>
     </row>
     <row r="67">
       <c r="A67">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C67" t="str">
-        <v>korea rain</v>
-      </c>
-      <c r="D67" t="str">
-        <v>outro</v>
-      </c>
-      <c r="E67" t="str">
-        <v>outro</v>
+        <v>save the day</v>
+      </c>
+      <c r="D67" s="1">
+        <v>0.0001497685185185185</v>
+      </c>
+      <c r="E67" s="1">
+        <v>0.00015486111111111112</v>
       </c>
       <c r="F67" t="str">
-        <v>black screen</v>
+        <v>Speaker 2</v>
       </c>
       <c r="G67" t="str">
-        <v>For real solutions …</v>
+        <v>All of us.</v>
+      </c>
+      <c r="H67">
+        <v>10</v>
       </c>
     </row>
     <row r="68">
       <c r="A68">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C68" t="str">
-        <v>korea rain</v>
-      </c>
-      <c r="D68" t="str">
-        <v>outro</v>
-      </c>
-      <c r="E68" t="str">
-        <v>outro</v>
+        <v>save the day</v>
+      </c>
+      <c r="D68" s="1">
+        <v>0.0001550925925925926</v>
+      </c>
+      <c r="E68" s="1">
+        <v>0.00016319444444444443</v>
       </c>
       <c r="F68" t="str">
-        <v>black screen</v>
+        <v>Speaker 2</v>
       </c>
       <c r="G68" t="str">
-        <v>Vote for Republican [Candidate X] on November 3</v>
+        <v>All of us.</v>
+      </c>
+      <c r="H68">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0</v>
+      </c>
+      <c r="C69" t="str">
+        <v>save the day</v>
+      </c>
+      <c r="D69" s="1">
+        <v>0.0001662037037037037</v>
+      </c>
+      <c r="E69" s="1">
+        <v>0.00021111111111111108</v>
+      </c>
+      <c r="F69" t="str">
+        <v>Speaker 1</v>
+      </c>
+      <c r="G69" t="str">
+        <v>We cannot pretend both sides are equally unfavorable.</v>
+      </c>
+      <c r="H69">
+        <v>53</v>
       </c>
     </row>
     <row r="70">
@@ -1613,19 +1746,22 @@
         <v>0</v>
       </c>
       <c r="C70" t="str">
-        <v>cheeseburger fail</v>
-      </c>
-      <c r="D70" t="str">
-        <v>title</v>
-      </c>
-      <c r="E70" t="str">
-        <v>title</v>
+        <v>save the day</v>
+      </c>
+      <c r="D70" s="1">
+        <v>0.0002122685185185185</v>
+      </c>
+      <c r="E70" s="1">
+        <v>0.00023240740740740738</v>
       </c>
       <c r="F70" t="str">
-        <v>meta data</v>
+        <v>Speaker 2</v>
       </c>
       <c r="G70" t="str">
-        <v>Losing patience with your leaders?</v>
+        <v>We can't say one vote doesn't matter.</v>
+      </c>
+      <c r="H70">
+        <v>37</v>
       </c>
     </row>
     <row r="71">
@@ -1633,19 +1769,22 @@
         <v>0</v>
       </c>
       <c r="C71" t="str">
-        <v>cheeseburger fail</v>
-      </c>
-      <c r="D71" t="str">
-        <v>description</v>
-      </c>
-      <c r="E71" t="str">
-        <v>description</v>
+        <v>save the day</v>
+      </c>
+      <c r="D71" s="1">
+        <v>0.00023333333333333333</v>
+      </c>
+      <c r="E71" s="1">
+        <v>0.00024236111111111114</v>
       </c>
       <c r="F71" t="str">
-        <v>meta data</v>
+        <v>Speaker 1</v>
       </c>
       <c r="G71" t="str">
-        <v>A fast food customer, representing voters, is finally fed up with the service he has received.</v>
+        <v>Your vote matters.</v>
+      </c>
+      <c r="H71">
+        <v>18</v>
       </c>
     </row>
     <row r="72">
@@ -1653,19 +1792,22 @@
         <v>0</v>
       </c>
       <c r="C72" t="str">
-        <v>cheeseburger fail</v>
-      </c>
-      <c r="D72" t="str">
-        <v>intro</v>
-      </c>
-      <c r="E72" t="str">
-        <v>intro</v>
+        <v>save the day</v>
+      </c>
+      <c r="D72" s="1">
+        <v>0.00024398148148148147</v>
+      </c>
+      <c r="E72" s="1">
+        <v>0.0002546296296296296</v>
       </c>
       <c r="F72" t="str">
-        <v>black screen</v>
+        <v>Speaker 2</v>
       </c>
       <c r="G72" t="str">
-        <v>[CandidateX] feels your pain.</v>
+        <v>Your vote matters.</v>
+      </c>
+      <c r="H72">
+        <v>18</v>
       </c>
     </row>
     <row r="73">
@@ -1673,16 +1815,22 @@
         <v>0</v>
       </c>
       <c r="C73" t="str">
-        <v>cheeseburger fail</v>
-      </c>
-      <c r="D73" t="str">
-        <v>:00</v>
-      </c>
-      <c r="E73" t="str">
-        <v>:31</v>
+        <v>save the day</v>
+      </c>
+      <c r="D73" s="1">
+        <v>0.0002564814814814815</v>
+      </c>
+      <c r="E73" s="1">
+        <v>0.0002666666666666667</v>
+      </c>
+      <c r="F73" t="str">
+        <v>Speaker 2</v>
       </c>
       <c r="G73" t="str">
-        <v>Man complains at fast food window</v>
+        <v>It affects everything.</v>
+      </c>
+      <c r="H73">
+        <v>22</v>
       </c>
     </row>
     <row r="74">
@@ -1690,19 +1838,22 @@
         <v>0</v>
       </c>
       <c r="C74" t="str">
-        <v>cheeseburger fail</v>
-      </c>
-      <c r="D74" t="str">
-        <v>outro</v>
-      </c>
-      <c r="E74" t="str">
-        <v>outro</v>
+        <v>save the day</v>
+      </c>
+      <c r="D74" s="1">
+        <v>0.00026828703703703704</v>
+      </c>
+      <c r="E74" s="1">
+        <v>0.0002863425925925926</v>
       </c>
       <c r="F74" t="str">
-        <v>black screen</v>
+        <v>Speaker 1</v>
       </c>
       <c r="G74" t="str">
-        <v>For competence you can count on …</v>
+        <v>See, this isn't just an election.</v>
+      </c>
+      <c r="H74">
+        <v>33</v>
       </c>
     </row>
     <row r="75">
@@ -1710,24 +1861,988 @@
         <v>0</v>
       </c>
       <c r="C75" t="str">
+        <v>save the day</v>
+      </c>
+      <c r="D75" s="1">
+        <v>0.0002895833333333333</v>
+      </c>
+      <c r="E75" s="1">
+        <v>0.0003018518518518518</v>
+      </c>
+      <c r="F75" t="str">
+        <v>Speaker 1</v>
+      </c>
+      <c r="G75" t="str">
+        <v>It's a tipping point.</v>
+      </c>
+      <c r="H75">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0</v>
+      </c>
+      <c r="C76" t="str">
+        <v>save the day</v>
+      </c>
+      <c r="D76" s="1">
+        <v>0.0003039351851851852</v>
+      </c>
+      <c r="E76" s="1">
+        <v>0.0003104166666666667</v>
+      </c>
+      <c r="F76" t="str">
+        <v>Speaker 2</v>
+      </c>
+      <c r="G76" t="str">
+        <v>For the country.</v>
+      </c>
+      <c r="H76">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0</v>
+      </c>
+      <c r="C77" t="str">
+        <v>save the day</v>
+      </c>
+      <c r="D77" s="1">
+        <v>0.00031319444444444445</v>
+      </c>
+      <c r="E77" s="1">
+        <v>0.00032175925925925926</v>
+      </c>
+      <c r="F77" t="str">
+        <v>Speaker 1</v>
+      </c>
+      <c r="G77" t="str">
+        <v>For the world.</v>
+      </c>
+      <c r="H77">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0</v>
+      </c>
+      <c r="C78" t="str">
+        <v>save the day</v>
+      </c>
+      <c r="D78" s="1">
+        <v>0.000324537037037037</v>
+      </c>
+      <c r="E78" s="1">
+        <v>0.00033194444444444444</v>
+      </c>
+      <c r="F78" t="str">
+        <v>Speaker 1</v>
+      </c>
+      <c r="G78" t="str">
+        <v>For your world.</v>
+      </c>
+      <c r="H78">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0</v>
+      </c>
+      <c r="C79" t="str">
+        <v>save the day</v>
+      </c>
+      <c r="D79" t="str">
+        <v>outro</v>
+      </c>
+      <c r="E79" t="str">
+        <v>outro</v>
+      </c>
+      <c r="F79" t="str">
+        <v>black screen</v>
+      </c>
+      <c r="G79" t="str">
+        <v>There's at least one thing we can agree on ...</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0</v>
+      </c>
+      <c r="C80" t="str">
+        <v>save the day</v>
+      </c>
+      <c r="D80" t="str">
+        <v>outro</v>
+      </c>
+      <c r="E80" t="str">
+        <v>outro</v>
+      </c>
+      <c r="F80" t="str">
+        <v>black screen</v>
+      </c>
+      <c r="G80" t="str">
+        <v>"We cannot pretend both sides are equally unfavorable."</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0</v>
+      </c>
+      <c r="C81" t="str">
+        <v>save the day</v>
+      </c>
+      <c r="D81" t="str">
+        <v>outro</v>
+      </c>
+      <c r="E81" t="str">
+        <v>outro</v>
+      </c>
+      <c r="F81" t="str">
+        <v>black screen</v>
+      </c>
+      <c r="G81" t="str">
+        <v>Vote for Republican [Candidate X] on November 3</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0</v>
+      </c>
+      <c r="C83" t="str">
+        <v>chicken little</v>
+      </c>
+      <c r="D83" t="str">
+        <v>title</v>
+      </c>
+      <c r="E83" t="str">
+        <v>title</v>
+      </c>
+      <c r="F83" t="str">
+        <v>meta data</v>
+      </c>
+      <c r="G83" t="str">
+        <v>The new star of the Democratic Party looks familiar</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>3</v>
+      </c>
+      <c r="C84" t="str">
+        <v>chicken little</v>
+      </c>
+      <c r="D84" t="str">
+        <v>description</v>
+      </c>
+      <c r="E84" t="str">
+        <v>description</v>
+      </c>
+      <c r="F84" t="str">
+        <v>meta data</v>
+      </c>
+      <c r="G84" t="str">
+        <v>Border walls are useless when the enemy is within, as these clips from the 1943 Disney cartoon Chicken Little illustrate.</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0</v>
+      </c>
+      <c r="C85" t="str">
+        <v>chicken little</v>
+      </c>
+      <c r="D85" s="1">
+        <v>0.000019791666666666665</v>
+      </c>
+      <c r="E85" s="1">
+        <v>0.00018020833333333333</v>
+      </c>
+      <c r="F85" t="str">
+        <v>Speaker 1</v>
+      </c>
+      <c r="G85" t="str">
+        <v>Our story takes place in a nice cozy little farmyard as our story continues We find all our fine-feathered friends happy and contented and why not didn't they have a big strong fence protecting them?</v>
+      </c>
+      <c r="H85">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0</v>
+      </c>
+      <c r="C86" t="str">
+        <v>chicken little</v>
+      </c>
+      <c r="D86" s="1">
+        <v>0.00018622685185185186</v>
+      </c>
+      <c r="E86" s="1">
+        <v>0.00019618055555555553</v>
+      </c>
+      <c r="F86" t="str">
+        <v>Speaker 2</v>
+      </c>
+      <c r="G86" t="str">
+        <v>But wait a minute.</v>
+      </c>
+      <c r="H86">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0</v>
+      </c>
+      <c r="C87" t="str">
+        <v>chicken little</v>
+      </c>
+      <c r="D87" s="1">
+        <v>0.00020289351851851854</v>
+      </c>
+      <c r="E87" s="1">
+        <v>0.0002119212962962963</v>
+      </c>
+      <c r="F87" t="str">
+        <v>Speaker 1</v>
+      </c>
+      <c r="G87" t="str">
+        <v>What's this?</v>
+      </c>
+      <c r="H87">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0</v>
+      </c>
+      <c r="C88" t="str">
+        <v>chicken little</v>
+      </c>
+      <c r="D88" s="1">
+        <v>0.0002643518518518518</v>
+      </c>
+      <c r="E88" s="1">
+        <v>0.0003881944444444444</v>
+      </c>
+      <c r="F88" t="str">
+        <v>Speaker 1</v>
+      </c>
+      <c r="G88" t="str">
+        <v>It's foxy loxy the poultry fancier Looks like he's taken an interest in our little community a culinary interest So why doesn't he just jump in and help himself?</v>
+      </c>
+      <c r="H88">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0</v>
+      </c>
+      <c r="C89" t="str">
+        <v>chicken little</v>
+      </c>
+      <c r="D89" s="1">
+        <v>0.0003881944444444444</v>
+      </c>
+      <c r="E89" s="1">
+        <v>0.0004817129629629629</v>
+      </c>
+      <c r="F89" t="str">
+        <v>Speaker 1</v>
+      </c>
+      <c r="G89" t="str">
+        <v>Do you suppose it's because of the high fence or the locks on the inside or the farmers shotgun?</v>
+      </c>
+      <c r="H89">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0</v>
+      </c>
+      <c r="C90" t="str">
+        <v>chicken little</v>
+      </c>
+      <c r="D90" s="1">
+        <v>0.0004974537037037036</v>
+      </c>
+      <c r="E90" s="1">
+        <v>0.0006237268518518519</v>
+      </c>
+      <c r="F90" t="str">
+        <v>Speaker 1</v>
+      </c>
+      <c r="G90" t="str">
+        <v>But I'm not a fox for nothing besides there's more than one way to plug a chicken Psychology why should I just get one when I can get them all?</v>
+      </c>
+      <c r="H90">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0</v>
+      </c>
+      <c r="C91" t="str">
+        <v>chicken little</v>
+      </c>
+      <c r="D91" s="1">
+        <v>0.0006393518518518519</v>
+      </c>
+      <c r="E91" s="1">
+        <v>0.0006939814814814815</v>
+      </c>
+      <c r="F91" t="str">
+        <v>Speaker 1</v>
+      </c>
+      <c r="G91" t="str">
+        <v>Quote to influence the masses aim first at the least intelligent unquote</v>
+      </c>
+      <c r="H91">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>3</v>
+      </c>
+      <c r="C92" t="str">
+        <v>chicken little</v>
+      </c>
+      <c r="D92" t="str">
+        <v>outro</v>
+      </c>
+      <c r="E92" t="str">
+        <v>outro</v>
+      </c>
+      <c r="F92" t="str">
+        <v>black screen</v>
+      </c>
+      <c r="G92" t="str">
+        <v>Vote as if your life depends on it.</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>3</v>
+      </c>
+      <c r="C93" t="str">
+        <v>chicken little</v>
+      </c>
+      <c r="D93" t="str">
+        <v>outro</v>
+      </c>
+      <c r="E93" t="str">
+        <v>outro</v>
+      </c>
+      <c r="F93" t="str">
+        <v>black screen</v>
+      </c>
+      <c r="G93" t="str">
+        <v>Vote for Republican [Candidate X] on November 3</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>3</v>
+      </c>
+      <c r="C95" t="str">
+        <v>korea rain</v>
+      </c>
+      <c r="D95" t="str">
+        <v>title</v>
+      </c>
+      <c r="E95" t="str">
+        <v>title</v>
+      </c>
+      <c r="F95" t="str">
+        <v>meta data</v>
+      </c>
+      <c r="G95" t="str">
+        <v>Impressed with your leaders?</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>3</v>
+      </c>
+      <c r="C96" t="str">
+        <v>korea rain</v>
+      </c>
+      <c r="D96" t="str">
+        <v>description</v>
+      </c>
+      <c r="E96" t="str">
+        <v>description</v>
+      </c>
+      <c r="F96" t="str">
+        <v>meta data</v>
+      </c>
+      <c r="G96" t="str">
+        <v>A man tries to impress a woman with an idea for protecting her from the rain. She has the real solution.</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>3</v>
+      </c>
+      <c r="C97" t="str">
+        <v>korea rain</v>
+      </c>
+      <c r="D97" t="str">
+        <v>intro</v>
+      </c>
+      <c r="E97" t="str">
+        <v>intro</v>
+      </c>
+      <c r="F97" t="str">
+        <v>black screen</v>
+      </c>
+      <c r="G97" t="str">
+        <v>Democrat [CandidateX] wants to impress you.</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>3</v>
+      </c>
+      <c r="C98" t="str">
+        <v>korea rain</v>
+      </c>
+      <c r="D98" s="1">
+        <v>0.000013541666666666666</v>
+      </c>
+      <c r="E98" s="1">
+        <v>0.000023495370370370367</v>
+      </c>
+      <c r="F98" t="str">
+        <v>Speaker 1</v>
+      </c>
+      <c r="G98" t="str">
+        <v>Why is it raining all of a sudden?</v>
+      </c>
+      <c r="H98">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>3</v>
+      </c>
+      <c r="C99" t="str">
+        <v>korea rain</v>
+      </c>
+      <c r="D99" s="1">
+        <v>0.000028587962962962966</v>
+      </c>
+      <c r="E99" s="1">
+        <v>0.000041782407407407405</v>
+      </c>
+      <c r="F99" t="str">
+        <v>Speaker 1</v>
+      </c>
+      <c r="G99" t="str">
+        <v>There wasn't any forecast today.</v>
+      </c>
+      <c r="H99">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>3</v>
+      </c>
+      <c r="C100" t="str">
+        <v>korea rain</v>
+      </c>
+      <c r="D100" s="1">
+        <v>0.00004479166666666667</v>
+      </c>
+      <c r="E100" s="1">
+        <v>0.00004756944444444445</v>
+      </c>
+      <c r="F100" t="str">
+        <v>Speaker 2</v>
+      </c>
+      <c r="G100" t="str">
+        <v>I know.</v>
+      </c>
+      <c r="H100">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>3</v>
+      </c>
+      <c r="C101" t="str">
+        <v>korea rain</v>
+      </c>
+      <c r="D101" s="1">
+        <v>0.000060532407407407414</v>
+      </c>
+      <c r="E101" s="1">
+        <v>0.00006840277777777778</v>
+      </c>
+      <c r="F101" t="str">
+        <v>Speaker 1</v>
+      </c>
+      <c r="G101" t="str">
+        <v>Why is it raining all of a sudden?</v>
+      </c>
+      <c r="H101">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102">
+        <v>3</v>
+      </c>
+      <c r="C102" t="str">
+        <v>korea rain</v>
+      </c>
+      <c r="D102" s="1">
+        <v>0.00008229166666666667</v>
+      </c>
+      <c r="E102" s="1">
+        <v>0.00018703703703703704</v>
+      </c>
+      <c r="F102" t="str">
+        <v>Speaker 1</v>
+      </c>
+      <c r="G102" t="str">
+        <v>Should we run together?</v>
+      </c>
+      <c r="H102">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103">
+        <v>3</v>
+      </c>
+      <c r="C103" t="str">
+        <v>korea rain</v>
+      </c>
+      <c r="D103" s="1">
+        <v>0.00019212962962962963</v>
+      </c>
+      <c r="E103" s="1">
+        <v>0.00020555555555555559</v>
+      </c>
+      <c r="F103" t="str">
+        <v>Speaker 2</v>
+      </c>
+      <c r="G103" t="str">
+        <v>We shouldn't run together.</v>
+      </c>
+      <c r="H103">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104">
+        <v>3</v>
+      </c>
+      <c r="C104" t="str">
+        <v>korea rain</v>
+      </c>
+      <c r="D104" s="1">
+        <v>0.00021319444444444446</v>
+      </c>
+      <c r="E104" s="1">
+        <v>0.00021666666666666666</v>
+      </c>
+      <c r="F104" t="str">
+        <v>Speaker 2</v>
+      </c>
+      <c r="G104" t="str">
+        <v>Okay.</v>
+      </c>
+      <c r="H104">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105">
+        <v>3</v>
+      </c>
+      <c r="C105" t="str">
+        <v>korea rain</v>
+      </c>
+      <c r="D105" t="str">
+        <v>outro</v>
+      </c>
+      <c r="E105" t="str">
+        <v>outro</v>
+      </c>
+      <c r="F105" t="str">
+        <v>black screen</v>
+      </c>
+      <c r="G105" t="str">
+        <v>For real solutions …</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106">
+        <v>3</v>
+      </c>
+      <c r="C106" t="str">
+        <v>korea rain</v>
+      </c>
+      <c r="D106" t="str">
+        <v>outro</v>
+      </c>
+      <c r="E106" t="str">
+        <v>outro</v>
+      </c>
+      <c r="F106" t="str">
+        <v>black screen</v>
+      </c>
+      <c r="G106" t="str">
+        <v>Vote for Republican [Candidate X] on November 3</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108">
+        <v>0</v>
+      </c>
+      <c r="C108" t="str">
         <v>cheeseburger fail</v>
       </c>
-      <c r="D75" t="str">
-        <v>outro</v>
-      </c>
-      <c r="E75" t="str">
-        <v>outro</v>
-      </c>
-      <c r="F75" t="str">
+      <c r="D108" t="str">
+        <v>title</v>
+      </c>
+      <c r="E108" t="str">
+        <v>title</v>
+      </c>
+      <c r="F108" t="str">
+        <v>meta data</v>
+      </c>
+      <c r="G108" t="str">
+        <v>Losing patience with your leaders?</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109">
+        <v>0</v>
+      </c>
+      <c r="C109" t="str">
+        <v>cheeseburger fail</v>
+      </c>
+      <c r="D109" t="str">
+        <v>description</v>
+      </c>
+      <c r="E109" t="str">
+        <v>description</v>
+      </c>
+      <c r="F109" t="str">
+        <v>meta data</v>
+      </c>
+      <c r="G109" t="str">
+        <v>A fast food customer, representing voters, is finally fed up with the service he has received.</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110">
+        <v>0</v>
+      </c>
+      <c r="C110" t="str">
+        <v>cheeseburger fail</v>
+      </c>
+      <c r="D110" t="str">
+        <v>intro</v>
+      </c>
+      <c r="E110" t="str">
+        <v>intro</v>
+      </c>
+      <c r="F110" t="str">
         <v>black screen</v>
       </c>
-      <c r="G75" t="str">
+      <c r="G110" t="str">
+        <v>[CandidateX] feels your pain.</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111">
+        <v>0</v>
+      </c>
+      <c r="C111" t="str">
+        <v>cheeseburger fail</v>
+      </c>
+      <c r="D111" s="1">
+        <v>0</v>
+      </c>
+      <c r="E111" s="1">
+        <v>0.00002962962962962963</v>
+      </c>
+      <c r="F111" t="str">
+        <v>Speaker 1</v>
+      </c>
+      <c r="G111" t="str">
+        <v>When you have a cheeseburger, you have a cheeseburger.</v>
+      </c>
+      <c r="H111">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112">
+        <v>0</v>
+      </c>
+      <c r="C112" t="str">
+        <v>cheeseburger fail</v>
+      </c>
+      <c r="D112" s="1">
+        <v>0.00003263888888888889</v>
+      </c>
+      <c r="E112" s="1">
+        <v>0.00005092592592592593</v>
+      </c>
+      <c r="F112" t="str">
+        <v>Speaker 1</v>
+      </c>
+      <c r="G112" t="str">
+        <v>If you have hamburger, you have hamburger.</v>
+      </c>
+      <c r="H112">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113">
+        <v>0</v>
+      </c>
+      <c r="C113" t="str">
+        <v>cheeseburger fail</v>
+      </c>
+      <c r="D113" s="1">
+        <v>0.00006157407407407408</v>
+      </c>
+      <c r="E113" s="1">
+        <v>0.0001076388888888889</v>
+      </c>
+      <c r="F113" t="str">
+        <v>Speaker 2</v>
+      </c>
+      <c r="G113" t="str">
+        <v>I want my money back, I want my money back now, and I want it fast.</v>
+      </c>
+      <c r="H113">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114">
+        <v>0</v>
+      </c>
+      <c r="C114" t="str">
+        <v>cheeseburger fail</v>
+      </c>
+      <c r="D114" s="1">
+        <v>0.00010972222222222222</v>
+      </c>
+      <c r="E114" s="1">
+        <v>0.00015162037037037037</v>
+      </c>
+      <c r="F114" t="str">
+        <v>Speaker 2</v>
+      </c>
+      <c r="G114" t="str">
+        <v>There's not even bacon on this and not onion on this and not anything that I asked for.</v>
+      </c>
+      <c r="H114">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115">
+        <v>0</v>
+      </c>
+      <c r="C115" t="str">
+        <v>cheeseburger fail</v>
+      </c>
+      <c r="D115" s="1">
+        <v>0.00015717592592592592</v>
+      </c>
+      <c r="E115" s="1">
+        <v>0.00018217592592592593</v>
+      </c>
+      <c r="F115" t="str">
+        <v>Speaker 2</v>
+      </c>
+      <c r="G115" t="str">
+        <v>This is such incompetence, I cannot believe it.</v>
+      </c>
+      <c r="H115">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116">
+        <v>0</v>
+      </c>
+      <c r="C116" t="str">
+        <v>cheeseburger fail</v>
+      </c>
+      <c r="D116" s="1">
+        <v>0.0001837962962962963</v>
+      </c>
+      <c r="E116" s="1">
+        <v>0.0002016203703703704</v>
+      </c>
+      <c r="F116" t="str">
+        <v>Speaker 2</v>
+      </c>
+      <c r="G116" t="str">
+        <v>It happens every time I come here.</v>
+      </c>
+      <c r="H116">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117">
+        <v>0</v>
+      </c>
+      <c r="C117" t="str">
+        <v>cheeseburger fail</v>
+      </c>
+      <c r="D117" s="1">
+        <v>0.00020509259259259257</v>
+      </c>
+      <c r="E117" s="1">
+        <v>0.0002622685185185185</v>
+      </c>
+      <c r="F117" t="str">
+        <v>Speaker 2</v>
+      </c>
+      <c r="G117" t="str">
+        <v>I'm losing my s*** because this happened the past three times I've come.</v>
+      </c>
+      <c r="H117">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118">
+        <v>0</v>
+      </c>
+      <c r="C118" t="str">
+        <v>cheeseburger fail</v>
+      </c>
+      <c r="D118" s="1">
+        <v>0.0002696759259259259</v>
+      </c>
+      <c r="E118" s="1">
+        <v>0.00030138888888888885</v>
+      </c>
+      <c r="F118" t="str">
+        <v>Speaker 2</v>
+      </c>
+      <c r="G118" t="str">
+        <v>Please be competent once in your life.</v>
+      </c>
+      <c r="H118">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119">
+        <v>0</v>
+      </c>
+      <c r="C119" t="str">
+        <v>cheeseburger fail</v>
+      </c>
+      <c r="D119" s="1">
+        <v>0.00030902777777777775</v>
+      </c>
+      <c r="E119" s="1">
+        <v>0.00031435185185185185</v>
+      </c>
+      <c r="F119" t="str">
+        <v>Speaker 2</v>
+      </c>
+      <c r="G119" t="str">
+        <v>Once.</v>
+      </c>
+      <c r="H119">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120">
+        <v>0</v>
+      </c>
+      <c r="C120" t="str">
+        <v>cheeseburger fail</v>
+      </c>
+      <c r="D120" s="1">
+        <v>0.0003212962962962963</v>
+      </c>
+      <c r="E120" s="1">
+        <v>0.00034166666666666666</v>
+      </c>
+      <c r="F120" t="str">
+        <v>Speaker 2</v>
+      </c>
+      <c r="G120" t="str">
+        <v>Take an order and fill it.</v>
+      </c>
+      <c r="H120">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121">
+        <v>0</v>
+      </c>
+      <c r="C121" t="str">
+        <v>cheeseburger fail</v>
+      </c>
+      <c r="D121" t="str">
+        <v>outro</v>
+      </c>
+      <c r="E121" t="str">
+        <v>outro</v>
+      </c>
+      <c r="F121" t="str">
+        <v>black screen</v>
+      </c>
+      <c r="G121" t="str">
+        <v>For competence you can count on …</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122">
+        <v>0</v>
+      </c>
+      <c r="C122" t="str">
+        <v>cheeseburger fail</v>
+      </c>
+      <c r="D122" t="str">
+        <v>outro</v>
+      </c>
+      <c r="E122" t="str">
+        <v>outro</v>
+      </c>
+      <c r="F122" t="str">
+        <v>black screen</v>
+      </c>
+      <c r="G122" t="str">
         <v>Vote for Republican [Candidate X] on November 3</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K76"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K123"/>
   </ignoredErrors>
 </worksheet>
 </file>